--- a/docs/Vero7878_track2_methods.xlsx
+++ b/docs/Vero7878_track2_methods.xlsx
@@ -542,9 +542,9 @@
         <is>
           <t>Mechanism-first, falsification-first, and audited.
 Curation. Each lead was sent to an independent adversarial review instructed to REFUTE it, not to support it. A single-standard re-score was then applied to remove survivorship bias. One consequence worth naming: our earlier lead candidate, 4-PBA, was demoted to INSUFFICIENT on mechanism (its action is secretory-cargo export via COPII sorting, not cytosolic chaperoning, with zero BUBR1-specific data), and that demotion is carried consistently across report, pitch, candidate table and submission record.
-Citation discipline. Every load-bearing citation is resolved against Europe PMC by scripts/phase1/16_verify_citations.py, which compares the returned title with the one we recorded. 35 load-bearing PMIDs, zero unresolved mismatches. A separate human verification pass re-read the primary texts and is recorded with its own access limits in registers/citation_manual_check_2026-10-19b.md. That pass removed one miscited source from the mechanism chain and downgraded one edge from 'measured' to 'asserted' because the source's human result is the authors' stated prediction, not a measurement.
+Citation discipline. Every load-bearing citation is resolved against Europe PMC by scripts/phase1/16_verify_citations.py, which compares the returned title with the one we recorded. 36 load-bearing PMIDs, zero unresolved mismatches. A separate human verification pass re-read the primary texts and is recorded with its own access limits in registers/citation_manual_check_2026-10-19b.md. That pass removed one miscited source from the mechanism chain and downgraded one edge from 'measured' to 'asserted' because the source's human result is the authors' stated prediction, not a measurement.
 One citation is carried at a strength we would normally reject, and we flag it rather than hide it: for the SIRT2-K250 link the publisher deposited no abstract and we could not obtain the full text, so it is graded 'asserted', cited for direction only, and no result is quoted from it. We judged that disclosing a load-bearing COUNTER-argument we could not fully verify was better than omitting the counter-argument.
-Claim ledger. Every statement that affects the conclusion has a row in registers/claim_ledger.csv (36 claims: 18 mechanism, 11 regulatory, 5 global-negative, 2 method), each with source URL, locator, checked date, evidence strength, counter-evidence and disposition. The ledger is GENERATED from the mechanism chain and the eligibility matrix on every clean run, not hand-maintained, so a claim cannot drift away from its source. The five global-negative claims — the 'no approved drug does X' statements that one counterexample would destroy — each carry a dated, reproducible search in registers/search_strategies.md with the verbatim query, the hits, and why each hit does not count.</t>
+Claim ledger. Every statement that affects the conclusion has a row in registers/claim_ledger.csv (37 claims: 18 mechanism, 12 regulatory, 5 global-negative, 2 method), each with source URL, locator, checked date, evidence strength, counter-evidence and disposition. The ledger is GENERATED from the mechanism chain and the eligibility matrix on every clean run, not hand-maintained, so a claim cannot drift away from its source. The five global-negative claims — the 'no approved drug does X' statements that one counterexample would destroy — each carry a dated, reproducible search in registers/search_strategies.md with the verbatim query, the hits, and why each hit does not count.</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         <is>
           <t>Regulatory / product level
 - DailyMed (FDA Structured Product Labels) — the load-bearing source for product eligibility. Labels opened and quoted verbatim with their revision dates, including niacin extended-release (setid 6e604319-e164-4056-ab80-b78b98c519c7, revised 12/2025), niacin immediate-release (Niacor), Buphenyl, Ravicti, Acetadote, sirolimus, metformin.
-- EMA EPAR — Translarna (ataluren): conditional marketing authorisation NOT renewed on 28 March 2025 because effectiveness was not confirmed. This closes the readthrough route for the truncating allele.
+- EMA EPAR — Translarna (ataluren): conditional marketing authorisation NOT renewed on 28 March 2025 because effectiveness was not confirmed. We first read this as closing the readthrough route; it does not. Ataluren retains a Great Britain marketing authorisation (live UK SmPC, 250 mg dated 2026-03-31, checked 2026-10-20), for a different gene and indication, so the bounded statement is that no approved readthrough agent is eligible for this allele rather than that none exists.
 - NIH Office of Dietary Supplements — for NMN and NR, which are supplements rather than approved drugs. These rows are marked in the matrix as landing pages with no product label, because the ABSENCE of a label is exactly what the row records.
 Target / tractability
 - Open Targets Platform, target ENSG00000156970 (BUB1B), data version 26.09, queried 2026-10-19 — tractability across small molecule, antibody, PROTAC and other-clinical modalities.

--- a/docs/Vero7878_track2_methods.xlsx
+++ b/docs/Vero7878_track2_methods.xlsx
@@ -491,7 +491,7 @@
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>We fixed the mechanism and the therapeutic objective BEFORE looking at any drug, so that candidates could not steer the biology.
-1. Variant -&gt; mechanism. The two BUB1B alleles come from our own Track 1 submission (full match at rank 1 on the leaderboard), not from a database lookup: neither allele has a ClinVar record in the 2026-10-04 release, so there was nothing to look up. Transcript-level facts (consequence, exon, NMD call, protein position) were computed twice by independent routes — Ensembl VEP 116 offline, and our own arithmetic over the Ensembl 116 GTF — and a disagreement blocks the pipeline rather than being resolved silently.
+1. Variant -&gt; mechanism. The two BUB1B alleles come from our own Track 1 submission (full match at rank 1 on the leaderboard), and the transcript-level facts below were computed rather than copied. Corrected 2026-10-21: an earlier version of this form said neither allele has a ClinVar record. The truncating allele does have one (VCV000533901, Pathogenic/Likely pathogenic, criteria provided / multiple submitters / no conflicts, condition includes mosaic variegated aneuploidy syndrome 1); the missense allele's exact nucleotide change does not. Transcript-level facts (consequence, exon, NMD call, protein position) were computed twice by independent routes — Ensembl VEP 116 offline, and our own arithmetic over the Ensembl 116 GTF — and a disagreement blocks the pipeline rather than being resolved silently.
 2. Mechanism -&gt; a measurable bottleneck. We built an explicit causal chain (docs/mechanism_graph.yaml, 20 nodes / 18 edges). Every edge carries an evidence strength (measured_in_proband / measured_in_model / predicted / asserted), the model system and species it was measured in, a genotype_match field saying how far the evidence is from this child's allele, sourced citations with locators, and a counter-evidence field. An edge with no source cannot exist, and a phenotype the chain cannot explain is listed as unexplained rather than joined by an assertion (two of eight are).
 3. Objective, then candidates. The chain identifies residual BubR1 abundance and checkpoint function as the bottleneck. The therapeutic objective is stated as a measurable endpoint, not 'improve the disease'. Only then were candidates considered, each declaring which objective class it claims to serve (restore / mitigate / deselect / protect).
 4. Screening. A small disease-agnostic engine (src/triage.py) applies a directionality prerequisite and four patient constraint gates read from a case manifest. It computes a GATE VERDICT ONLY; the scientific disposition is a separate human judgment, and the two are printed side by side (docs/computed_vs_human.md) so the tool never masquerades as science. Unknown or malformed inputs BLOCK rather than passing.
@@ -579,7 +579,7 @@
 - PubMed / Europe PMC — all 35 load-bearing citations resolved programmatically with title verification; dated search strategies for every global-negative claim.
 Variant / protein annotation
 - Ensembl VEP 116 (offline, matching cache) and the Ensembl 116 GTF, run as two independent methods and cross-checked field by field; calibrated against 400 public ClinVar pathogenic/likely-pathogenic variants before being applied to the case variants.
-- ClinVar release 2026-10-04 — exact-coordinate overlay (result: neither allele has a record).
+- ClinVar release 2026-10-04, corrected 2026-10-21 by a gene-level ClinVar query matched locally: the truncating allele IS recorded (VCV000533901, Pathogenic/Likely pathogenic, two-star review, names mosaic variegated aneuploidy syndrome 1); the missense allele's exact nucleotide change is not recorded (the same amino-acid change by a different nucleotide is VCV004600147, uncertain significance). Why the original overlay returned nothing is open, and is recorded as open.
 - UniProt O60566 and AlphaFold AF-O60566-F1 for domain placement and per-residue confidence.
 Not used, and disclosed as a recall limitation: DrugBank, ChEMBL, DGIdb and connectivity-map data were NOT screened systematically. Candidate generation was literature-driven.</t>
         </is>
@@ -635,7 +635,7 @@
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>We treat repurposing for an N-of-1 rare disease as a problem of DISCIPLINE, not search. The deliverable is a decision rule, and under it one named conditional candidate.
-Method. The two BUB1B alleles come from our own Track 1 result (rank-1 full match), not a lookup — neither has a ClinVar record, so the pathogenicity argument cannot lean on curation. Transcript facts are computed twice by independent routes; a disagreement blocks the pipeline. The mechanism is held as an explicit causal chain: 18 edges, each with an evidence strength, the species and system it was measured in, how far that evidence sits from this child's allele, sourced citations with locators, and counter-evidence. An edge without a source cannot exist; two of eight registered phenotypes are left UNEXPLAINED rather than connected by assertion. The chain identifies residual BubR1 abundance and checkpoint function as the bottleneck; the therapeutic objective is a measurable endpoint. A small disease-agnostic engine applies a directionality prerequisite and four patient constraint gates, producing a GATE verdict only; the scientific disposition stays a separate human judgment, printed beside it. Eligibility is a property of a PRODUCT (molecule x form x jurisdiction x indication x age x status x date x openable URL), not a molecule. Because residual function is unmeasured, the engine runs against three residual-function scenarios.
+Method. The two BUB1B alleles come from our own Track 1 result (rank-1 full match), and the transcript facts are computed, not copied. Corrected 2026-10-21: the truncating allele does carry a two-star Pathogenic/Likely pathogenic ClinVar record naming mosaic variegated aneuploidy syndrome 1 (VCV000533901); the missense allele's exact change carries none, so that half of the argument does not lean on curation. Transcript facts are computed twice by independent routes; a disagreement blocks the pipeline. The mechanism is held as an explicit causal chain: 18 edges, each with an evidence strength, the species and system it was measured in, how far that evidence sits from this child's allele, sourced citations with locators, and counter-evidence. An edge without a source cannot exist; two of eight registered phenotypes are left UNEXPLAINED rather than connected by assertion. The chain identifies residual BubR1 abundance and checkpoint function as the bottleneck; the therapeutic objective is a measurable endpoint. A small disease-agnostic engine applies a directionality prerequisite and four patient constraint gates, producing a GATE verdict only; the scientific disposition stays a separate human judgment, printed beside it. Eligibility is a property of a PRODUCT (molecule x form x jurisdiction x indication x age x status x date x openable URL), not a molecule. Because residual function is unmeasured, the engine runs against three residual-function scenarios.
 Result. Niacin (nicotinic acid), an approved prescription NAD+ precursor acting through the SIRT2-BubR1 stabilization axis, carried as CONDITIONAL. It holds only under one of three scenarios; the scenario file gives them equal prior weight, so by our own numbers its objective class has about a one-in-three chance of being directionally invalid. We also report, as a FINDING, that the strongest mechanistic link — directly stabilising BubR1 or selectively activating SIRT2 — has no approved drug.
 Strengths. Every load-bearing number in the report is recomputed from source by a release gate that refuses to publish on a mismatch; it has caught us. The claim ledger is generated, not typed. The engine reports the safety axes its own gates structurally CANNOT see, so a gate PASS can never read as 'no risk'. Twenty-eight self-tests pin its edges. The decisive experiment is also DIAGNOSTIC: it places residual BubR1 on a published dose-phenotype map, informing prognosis independent of any drug.
 Limitations, stated plainly. Candidate generation was literature-driven, not a database sweep, so recall is not claimed. The decision rule was written alongside the candidate work rather than pre-registered. No NAD+ booster has been tested in an MVA model or in cells of this allele class, and NAD+ status in MVA has never been measured, so the deficiency the intervention would correct has not been shown to exist. SIRT2 acts on BubR1 at more than one lysine with OPPOSITE consequences for stability, and the net effect in this background is unmeasured. There is no pediatric niacin label; the available pediatric series reports 38% discontinuation at overlapping doses. The oncology direction is unresolved. We specify the experiment; we do not perform it.</t>

--- a/docs/Vero7878_track2_methods.xlsx
+++ b/docs/Vero7878_track2_methods.xlsx
@@ -569,17 +569,18 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Regulatory / product level
+          <t xml:space="preserve">Regulatory / product level
 - DailyMed (FDA Structured Product Labels) — the load-bearing source for product eligibility. Labels opened and quoted verbatim with their revision dates, including niacin extended-release (setid 6e604319-e164-4056-ab80-b78b98c519c7, revised 12/2025), niacin immediate-release (Niacor), Buphenyl, Ravicti, Acetadote, sirolimus, metformin.
 - EMA EPAR — Translarna (ataluren): conditional marketing authorisation NOT renewed on 28 March 2025 because effectiveness was not confirmed. We first read this as closing the readthrough route; it does not. Ataluren retains a Great Britain marketing authorisation (live UK SmPC, 250 mg dated 2026-03-31, checked 2026-10-20), for a different gene and indication, so the bounded statement is that no approved readthrough agent is eligible for this allele rather than that none exists.
 - NIH Office of Dietary Supplements — for NMN and NR, which are supplements rather than approved drugs. These rows are marked in the matrix as landing pages with no product label, because the ABSENCE of a label is exactly what the row records.
 Target / tractability
-- Open Targets Platform, target ENSG00000156970 (BUB1B), data version 26.09, queried 2026-10-19 — tractability across small molecule, antibody, PROTAC and other-clinical modalities.
+- Open Targets Platform — tractability across small molecule, antibody, PROTAC and other-clinical modalities. Queried for target ENSG00000156970 (BUB1B) on 2026-10-19 (data 26.09), then widened on 2026-10-21 to the fifteen proteins of the checkpoint/segregation module, the two other MVA genes and the NAD+ axis, scripted and written as a dated snapshot (scripts/phase1/21_quant_checks.py tractability -&gt; docs/target_tractability.md). Counted result: none of the fifteen carries an approved drug in any modality; the five with advanced clinical small molecules are all inhibitors.
 Literature
-- PubMed / Europe PMC — all 35 load-bearing citations resolved programmatically with title verification; dated search strategies for every global-negative claim.
+- PubMed / Europe PMC — all 36 load-bearing citations resolved programmatically with title verification; dated search strategies for every global-negative claim.
 Variant / protein annotation
 - Ensembl VEP 116 (offline, matching cache) and the Ensembl 116 GTF, run as two independent methods and cross-checked field by field; calibrated against 400 public ClinVar pathogenic/likely-pathogenic variants before being applied to the case variants.
-- ClinVar release 2026-10-04, corrected 2026-10-21 by a gene-level ClinVar query matched locally: the truncating allele IS recorded (VCV000533901, Pathogenic/Likely pathogenic, two-star review, names mosaic variegated aneuploidy syndrome 1); the missense allele's exact nucleotide change is not recorded (the same amino-acid change by a different nucleotide is VCV004600147, uncertain significance). Why the original overlay returned nothing is open, and is recorded as open.
+- NCBI E-utilities (esearch/esummary, db=clinvar), gene-level query BUB1B[gene], 2026-10-21 — one row per VariationID, classified locally, giving the per-consequence base rates in docs/clinvar_baserate.md (1,426 of 1,498 missense records uncertain; 82 of 98 truncating records pathogenic or likely pathogenic). The query sends the gene symbol and nothing else.
+- ClinVar release 2026-10-04, corrected 2026-10-21 by that gene-level query matched locally: the truncating allele IS recorded (VCV000533901, Pathogenic/Likely pathogenic, two-star review, names mosaic variegated aneuploidy syndrome 1); the missense allele's exact nucleotide change is not recorded (the same amino-acid change by a different nucleotide is VCV004600147, uncertain significance). Why the original overlay returned nothing is open, and is recorded as open.
 - UniProt O60566 and AlphaFold AF-O60566-F1 for domain placement and per-residue confidence.
 Not used, and disclosed as a recall limitation: DrugBank, ChEMBL, DGIdb and connectivity-map data were NOT screened systematically. Candidate generation was literature-driven.</t>
         </is>
@@ -634,11 +635,11 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>We treat repurposing for an N-of-1 rare disease as a problem of DISCIPLINE, not search. The deliverable is a decision rule, and under it one named conditional candidate.
-Method. The two BUB1B alleles come from our own Track 1 result (rank-1 full match), and the transcript facts are computed, not copied. Corrected 2026-10-21: the truncating allele does carry a two-star Pathogenic/Likely pathogenic ClinVar record naming mosaic variegated aneuploidy syndrome 1 (VCV000533901); the missense allele's exact change carries none, so that half of the argument does not lean on curation. Transcript facts are computed twice by independent routes; a disagreement blocks the pipeline. The mechanism is held as an explicit causal chain: 18 edges, each with an evidence strength, the species and system it was measured in, how far that evidence sits from this child's allele, sourced citations with locators, and counter-evidence. An edge without a source cannot exist; two of eight registered phenotypes are left UNEXPLAINED rather than connected by assertion. The chain identifies residual BubR1 abundance and checkpoint function as the bottleneck; the therapeutic objective is a measurable endpoint. A small disease-agnostic engine applies a directionality prerequisite and four patient constraint gates, producing a GATE verdict only; the scientific disposition stays a separate human judgment, printed beside it. Eligibility is a property of a PRODUCT (molecule x form x jurisdiction x indication x age x status x date x openable URL), not a molecule. Because residual function is unmeasured, the engine runs against three residual-function scenarios.
-Result. Niacin (nicotinic acid), an approved prescription NAD+ precursor acting through the SIRT2-BubR1 stabilization axis, carried as CONDITIONAL. It holds only under one of three scenarios; the scenario file gives them equal prior weight, so by our own numbers its objective class has about a one-in-three chance of being directionally invalid. We also report, as a FINDING, that the strongest mechanistic link — directly stabilising BubR1 or selectively activating SIRT2 — has no approved drug.
-Strengths. Every load-bearing number in the report is recomputed from source by a release gate that refuses to publish on a mismatch; it has caught us. The claim ledger is generated, not typed. The engine reports the safety axes its own gates structurally CANNOT see, so a gate PASS can never read as 'no risk'. Twenty-eight self-tests pin its edges. The decisive experiment is also DIAGNOSTIC: it places residual BubR1 on a published dose-phenotype map, informing prognosis independent of any drug.
-Limitations, stated plainly. Candidate generation was literature-driven, not a database sweep, so recall is not claimed. The decision rule was written alongside the candidate work rather than pre-registered. No NAD+ booster has been tested in an MVA model or in cells of this allele class, and NAD+ status in MVA has never been measured, so the deficiency the intervention would correct has not been shown to exist. SIRT2 acts on BubR1 at more than one lysine with OPPOSITE consequences for stability, and the net effect in this background is unmeasured. There is no pediatric niacin label; the available pediatric series reports 38% discontinuation at overlapping doses. The oncology direction is unresolved. We specify the experiment; we do not perform it.</t>
+          <t xml:space="preserve">We treat N-of-1 repurposing as a problem of DISCIPLINE, not search. The deliverable is a decision rule, and under it one named conditional candidate.
+Method. The two BUB1B alleles come from our own Track 1 result (rank-1 full match); the transcript facts are computed twice by independent routes, and a disagreement blocks the pipeline. Corrected 2026-10-21: the truncating allele does carry a two-star Pathogenic/Likely pathogenic ClinVar record naming MVA1 (VCV000533901); the missense allele's exact change carries none, and 1,426 of 1,498 BUB1B missense records are uncertain, so curation discriminates almost nothing there. The mechanism is held as an explicit causal chain: 18 edges, each carrying its evidence strength, the system it was measured in, its distance from this child's allele, sourced citations with locators, and counter-evidence. An edge without a source cannot exist; two of eight registered phenotypes are left UNEXPLAINED rather than connected by assertion. The chain identifies residual BubR1 abundance and checkpoint function as the bottleneck; the therapeutic objective is a measurable endpoint. A disease-agnostic engine applies a directionality prerequisite and four patient constraint gates, producing a GATE verdict only; scientific disposition stays a separate human judgment, printed beside it. Eligibility is a property of a PRODUCT, not a molecule. Because residual function is unmeasured, the engine runs all three residual-function scenarios.
+Result. Niacin (nicotinic acid), an approved prescription NAD+ precursor acting through the SIRT2-BubR1 stabilization axis, carried as CONDITIONAL. It holds under only one of three equally weighted scenarios, so by our own numbers its objective class has about a one-in-three chance of being directionally invalid. We also report, as a FINDING, that the strongest mechanistic link - directly stabilising BubR1 or selectively activating SIRT2 - has no approved drug: of the fifteen proteins in this module and the NAD+ axis, none carries an approved drug, and the five with advanced clinical small molecules are all inhibitors.
+Strengths. Every load-bearing number is recomputed from source by a release gate that blocks on a mismatch; it has caught us, and the claim ledger is generated rather than typed. The engine reports the safety axes its gates structurally CANNOT see, so a PASS never reads as 'no risk'. The detectability of the proposed experiment is computed rather than asserted. The decisive experiment is also diagnostic: it places residual BubR1 on a published dose-phenotype map - a research-grade characterisation, not a validated prognostic test.
+Limitations, stated plainly. Candidate generation was literature-driven, not a database sweep, so recall is not claimed. The decision rule was written alongside the candidate work rather than pre-registered. No NAD+ booster has been tested in an MVA model or in cells of this allele class, and NAD+ status in MVA has never been measured. SIRT2 acts on BubR1 at two lysines with OPPOSITE consequences for stability, and the net effect in this background is unmeasured. There is no pediatric niacin label; the available pediatric series reports 38% discontinuation at overlapping doses. The oncology direction is unresolved. We specify the experiment; we do not perform it.</t>
         </is>
       </c>
     </row>
